--- a/るwords.xlsx
+++ b/るwords.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\苗欣奕的东西\折跃\Japanese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19BC7E1C-5DCC-4C0A-BC14-902E5FC16C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B52561C-90B3-4592-917E-F5AA0A449DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="特殊（とくしゅ）" sheetId="8" r:id="rId1"/>
@@ -6080,10 +6080,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>来月から大学の近くで一人暮らしを始める。つうがくのしやすさを考えて、大学まで歩いて通えるところにした</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>下个月开始我要在大学附近开始一个人生活，考虑到上学的便利性，我选择了一个可以走着就可以去上学的地方</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -8658,6 +8654,10 @@
   </si>
   <si>
     <t>同意，点头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>来月から大学の近くで一人暮らしを始める。通学の易さを考えて、大学まで歩いて通えるところにした</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10927,10 +10927,10 @@
     </row>
     <row r="3" spans="2:31" ht="18" x14ac:dyDescent="0.45">
       <c r="C3" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D3" t="s">
         <v>1786</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1787</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>102</v>
@@ -10939,34 +10939,34 @@
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>1775</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>1776</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>1777</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>1778</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>1779</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>1780</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>1781</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>1782</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>1783</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>1784</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>1785</v>
       </c>
       <c r="Q3" s="1"/>
       <c r="R3" s="6"/>
@@ -11056,7 +11056,7 @@
     </row>
     <row r="8" spans="2:31" ht="18" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>102</v>
@@ -11065,39 +11065,39 @@
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
+        <v>1678</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>1679</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>1680</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>1681</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>1682</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>1683</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>1684</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="N8" s="1" t="s">
         <v>1685</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="O8" s="1" t="s">
         <v>1686</v>
       </c>
-      <c r="O8" s="1" t="s">
+      <c r="P8" s="1" t="s">
         <v>1687</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>1688</v>
       </c>
     </row>
     <row r="9" spans="2:31" ht="18" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>102</v>
@@ -11106,34 +11106,34 @@
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
+        <v>1688</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>1689</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
+        <v>1691</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>1690</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>1692</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>1691</v>
-      </c>
       <c r="K9" s="1" t="s">
+        <v>1694</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>1695</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>1696</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>1697</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="O9" s="1" t="s">
         <v>1698</v>
       </c>
-      <c r="O9" s="1" t="s">
+      <c r="P9" s="1" t="s">
         <v>1699</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>1700</v>
       </c>
     </row>
     <row r="10" spans="2:31" ht="18" x14ac:dyDescent="0.45">
@@ -11650,10 +11650,10 @@
         <v>1443</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>2081</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>1444</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>1445</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>102</v>
@@ -11958,7 +11958,7 @@
     <row r="41" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A41" s="1"/>
       <c r="B41" s="2" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>737</v>
@@ -11967,34 +11967,34 @@
         <v>2</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="M41" t="s">
+        <v>1908</v>
+      </c>
+      <c r="N41" s="1" t="s">
         <v>1909</v>
       </c>
-      <c r="N41" s="1" t="s">
+      <c r="O41" s="1" t="s">
         <v>1910</v>
       </c>
-      <c r="O41" s="1" t="s">
+      <c r="P41" s="1" t="s">
         <v>1911</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>1912</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A42" s="1"/>
       <c r="B42" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>1906</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="D42" t="s">
         <v>1907</v>
-      </c>
-      <c r="D42" t="s">
-        <v>1908</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>266</v>
@@ -12003,22 +12003,22 @@
         <v>1</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="M42" s="1" t="s">
+        <v>1912</v>
+      </c>
+      <c r="N42" s="1" t="s">
         <v>1913</v>
       </c>
-      <c r="N42" s="1" t="s">
+      <c r="O42" s="1" t="s">
         <v>1914</v>
       </c>
-      <c r="O42" s="1" t="s">
+      <c r="P42" s="1" t="s">
         <v>1915</v>
-      </c>
-      <c r="P42" s="1" t="s">
-        <v>1916</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -12054,7 +12054,7 @@
         <v>1225</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -12233,7 +12233,7 @@
     </row>
     <row r="49" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B49" s="2" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="2"/>
@@ -12244,10 +12244,10 @@
         <v>2</v>
       </c>
       <c r="G49" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>1451</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>1452</v>
       </c>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
@@ -12256,13 +12256,13 @@
     </row>
     <row r="50" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B50" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>1454</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>1455</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>737</v>
@@ -12447,7 +12447,7 @@
         <v>47</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>266</v>
@@ -12537,13 +12537,13 @@
         <v>1161</v>
       </c>
       <c r="B59" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>1494</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="D59" t="s">
         <v>1495</v>
-      </c>
-      <c r="D59" t="s">
-        <v>1496</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>737</v>
@@ -12552,18 +12552,18 @@
         <v>1</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="60" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>1499</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>1500</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>721</v>
@@ -12572,21 +12572,21 @@
         <v>1</v>
       </c>
       <c r="G60" t="s">
+        <v>1496</v>
+      </c>
+      <c r="H60" s="1" t="s">
         <v>1497</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>1498</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>1507</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="D61" t="s">
         <v>1508</v>
-      </c>
-      <c r="D61" t="s">
-        <v>1509</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>737</v>
@@ -12595,27 +12595,27 @@
         <v>1</v>
       </c>
       <c r="G61" t="s">
+        <v>1500</v>
+      </c>
+      <c r="H61" s="1" t="s">
         <v>1501</v>
       </c>
-      <c r="H61" s="1" t="s">
+      <c r="M61" s="1" t="s">
         <v>1502</v>
       </c>
-      <c r="M61" s="1" t="s">
+      <c r="N61" s="1" t="s">
         <v>1503</v>
       </c>
-      <c r="N61" s="1" t="s">
+      <c r="O61" s="1" t="s">
         <v>1504</v>
       </c>
-      <c r="O61" s="1" t="s">
+      <c r="P61" s="1" t="s">
         <v>1505</v>
-      </c>
-      <c r="P61" s="1" t="s">
-        <v>1506</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>737</v>
@@ -12624,27 +12624,27 @@
         <v>1</v>
       </c>
       <c r="G62" s="14" t="s">
+        <v>1623</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>1624</v>
       </c>
-      <c r="H62" s="1" t="s">
-        <v>1625</v>
-      </c>
       <c r="M62" s="1" t="s">
+        <v>1730</v>
+      </c>
+      <c r="N62" s="1" t="s">
         <v>1731</v>
       </c>
-      <c r="N62" s="1" t="s">
+      <c r="O62" s="1" t="s">
         <v>1732</v>
       </c>
-      <c r="O62" s="1" t="s">
+      <c r="P62" s="1" t="s">
         <v>1733</v>
-      </c>
-      <c r="P62" s="1" t="s">
-        <v>1734</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>737</v>
@@ -12653,15 +12653,15 @@
         <v>1</v>
       </c>
       <c r="G63" t="s">
+        <v>1627</v>
+      </c>
+      <c r="H63" s="1" t="s">
         <v>1628</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>1629</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>737</v>
@@ -12670,27 +12670,27 @@
         <v>1</v>
       </c>
       <c r="G64" s="1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="H64" s="1" t="s">
         <v>1630</v>
       </c>
-      <c r="H64" s="1" t="s">
-        <v>1631</v>
-      </c>
       <c r="M64" s="1" t="s">
+        <v>1734</v>
+      </c>
+      <c r="N64" s="1" t="s">
         <v>1735</v>
       </c>
-      <c r="N64" s="1" t="s">
+      <c r="O64" s="1" t="s">
         <v>1736</v>
       </c>
-      <c r="O64" s="1" t="s">
+      <c r="P64" s="1" t="s">
         <v>1737</v>
-      </c>
-      <c r="P64" s="1" t="s">
-        <v>1738</v>
       </c>
     </row>
     <row r="65" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>737</v>
@@ -12699,27 +12699,27 @@
         <v>2</v>
       </c>
       <c r="G65" s="1" t="s">
+        <v>1728</v>
+      </c>
+      <c r="H65" s="1" t="s">
         <v>1729</v>
       </c>
-      <c r="H65" s="1" t="s">
-        <v>1730</v>
-      </c>
       <c r="M65" s="1" t="s">
+        <v>1738</v>
+      </c>
+      <c r="N65" s="1" t="s">
         <v>1739</v>
       </c>
-      <c r="N65" s="1" t="s">
+      <c r="O65" s="1" t="s">
         <v>1740</v>
       </c>
-      <c r="O65" s="1" t="s">
+      <c r="P65" s="1" t="s">
         <v>1741</v>
-      </c>
-      <c r="P65" s="1" t="s">
-        <v>1742</v>
       </c>
     </row>
     <row r="66" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>737</v>
@@ -12728,27 +12728,27 @@
         <v>1</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="N66" s="1" t="s">
+        <v>1749</v>
+      </c>
+      <c r="O66" s="1" t="s">
         <v>1750</v>
       </c>
-      <c r="O66" s="1" t="s">
-        <v>1751</v>
-      </c>
       <c r="P66" s="1" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>737</v>
@@ -12757,33 +12757,33 @@
         <v>1</v>
       </c>
       <c r="G67" s="1" t="s">
+        <v>1744</v>
+      </c>
+      <c r="H67" s="1" t="s">
         <v>1745</v>
       </c>
-      <c r="H67" s="1" t="s">
-        <v>1746</v>
-      </c>
       <c r="M67" s="1" t="s">
+        <v>1748</v>
+      </c>
+      <c r="N67" s="1" t="s">
         <v>1749</v>
       </c>
-      <c r="N67" s="1" t="s">
-        <v>1750</v>
-      </c>
       <c r="O67" s="1" t="s">
+        <v>1751</v>
+      </c>
+      <c r="P67" s="1" t="s">
         <v>1752</v>
-      </c>
-      <c r="P67" s="1" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="68" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="C68" t="s">
+        <v>1859</v>
+      </c>
+      <c r="D68" t="s">
         <v>1860</v>
-      </c>
-      <c r="D68" t="s">
-        <v>1861</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>737</v>
@@ -12792,33 +12792,33 @@
         <v>1</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="M68" s="1" t="s">
+        <v>1755</v>
+      </c>
+      <c r="N68" s="1" t="s">
         <v>1756</v>
       </c>
-      <c r="N68" s="1" t="s">
+      <c r="O68" s="1" t="s">
         <v>1757</v>
       </c>
-      <c r="O68" s="1" t="s">
+      <c r="P68" s="1" t="s">
         <v>1758</v>
-      </c>
-      <c r="P68" s="1" t="s">
-        <v>1759</v>
       </c>
     </row>
     <row r="69" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="C69" s="1" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D69" t="s">
         <v>1857</v>
-      </c>
-      <c r="D69" t="s">
-        <v>1858</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>737</v>
@@ -12827,30 +12827,30 @@
         <v>2</v>
       </c>
       <c r="G69" s="1" t="s">
+        <v>1850</v>
+      </c>
+      <c r="H69" s="1" t="s">
         <v>1851</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="M69" s="1" t="s">
         <v>1852</v>
       </c>
-      <c r="M69" s="1" t="s">
+      <c r="N69" s="1" t="s">
         <v>1853</v>
       </c>
-      <c r="N69" s="1" t="s">
+      <c r="O69" s="1" t="s">
         <v>1854</v>
       </c>
-      <c r="O69" s="1" t="s">
+      <c r="P69" s="1" t="s">
         <v>1855</v>
-      </c>
-      <c r="P69" s="1" t="s">
-        <v>1856</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C70" s="18" t="s">
         <v>1876</v>
-      </c>
-      <c r="C70" s="18" t="s">
-        <v>1877</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>737</v>
@@ -12859,21 +12859,21 @@
         <v>2</v>
       </c>
       <c r="G70" s="1" t="s">
+        <v>1873</v>
+      </c>
+      <c r="H70" s="1" t="s">
         <v>1874</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>1875</v>
       </c>
     </row>
     <row r="71" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="C71" t="s">
+        <v>1919</v>
+      </c>
+      <c r="D71" t="s">
         <v>1920</v>
-      </c>
-      <c r="D71" t="s">
-        <v>1921</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>1144</v>
@@ -12882,21 +12882,21 @@
         <v>2</v>
       </c>
       <c r="G71" s="1" t="s">
+        <v>1917</v>
+      </c>
+      <c r="H71" s="1" t="s">
         <v>1918</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>1919</v>
       </c>
     </row>
     <row r="72" spans="1:16" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C72" t="s" ph="1">
         <v>1953</v>
       </c>
-      <c r="C72" t="s" ph="1">
+      <c r="D72" t="s">
         <v>1954</v>
-      </c>
-      <c r="D72" t="s">
-        <v>1955</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>1144</v>
@@ -12905,27 +12905,27 @@
         <v>1</v>
       </c>
       <c r="G72" s="1" t="s">
+        <v>1949</v>
+      </c>
+      <c r="H72" s="1" t="s">
         <v>1950</v>
       </c>
-      <c r="H72" s="1" t="s">
-        <v>1951</v>
-      </c>
       <c r="M72" s="1" t="s">
+        <v>1957</v>
+      </c>
+      <c r="N72" s="1" t="s">
         <v>1958</v>
       </c>
-      <c r="N72" s="1" t="s">
-        <v>1959</v>
-      </c>
       <c r="O72" s="1" t="s">
+        <v>1955</v>
+      </c>
+      <c r="P72" s="1" t="s">
         <v>1956</v>
-      </c>
-      <c r="P72" s="1" t="s">
-        <v>1957</v>
       </c>
     </row>
     <row r="73" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>737</v>
@@ -12934,33 +12934,33 @@
         <v>2</v>
       </c>
       <c r="G73" s="1" t="s">
+        <v>1959</v>
+      </c>
+      <c r="H73" s="1" t="s">
         <v>1960</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="M73" s="1" t="s">
         <v>1961</v>
       </c>
-      <c r="M73" s="1" t="s">
+      <c r="N73" s="1" t="s">
         <v>1962</v>
       </c>
-      <c r="N73" s="1" t="s">
+      <c r="O73" s="1" t="s">
         <v>1963</v>
       </c>
-      <c r="O73" s="1" t="s">
+      <c r="P73" s="1" t="s">
         <v>1964</v>
-      </c>
-      <c r="P73" s="1" t="s">
-        <v>1965</v>
       </c>
     </row>
     <row r="74" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
+        <v>2037</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>2038</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="D74" t="s">
         <v>2039</v>
-      </c>
-      <c r="D74" t="s">
-        <v>2040</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>266</v>
@@ -12969,10 +12969,10 @@
         <v>1</v>
       </c>
       <c r="G74" s="1" t="s">
+        <v>2035</v>
+      </c>
+      <c r="H74" s="1" t="s">
         <v>2036</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>2037</v>
       </c>
       <c r="M74" s="1"/>
       <c r="N74" s="1"/>
@@ -12981,7 +12981,7 @@
     </row>
     <row r="75" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>737</v>
@@ -12990,33 +12990,33 @@
         <v>1</v>
       </c>
       <c r="G75" s="1" t="s">
+        <v>1988</v>
+      </c>
+      <c r="H75" s="1" t="s">
         <v>1989</v>
       </c>
-      <c r="H75" s="1" t="s">
-        <v>1990</v>
-      </c>
       <c r="I75" s="1" t="s">
+        <v>1991</v>
+      </c>
+      <c r="J75" s="1" t="s">
         <v>1992</v>
       </c>
-      <c r="J75" s="1" t="s">
+      <c r="M75" s="1" t="s">
         <v>1993</v>
       </c>
-      <c r="M75" s="1" t="s">
+      <c r="N75" s="1" t="s">
         <v>1994</v>
       </c>
-      <c r="N75" s="1" t="s">
+      <c r="O75" s="1" t="s">
         <v>1995</v>
       </c>
-      <c r="O75" s="1" t="s">
+      <c r="P75" s="1" t="s">
         <v>1996</v>
-      </c>
-      <c r="P75" s="1" t="s">
-        <v>1997</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>737</v>
@@ -13025,15 +13025,15 @@
         <v>1</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="77" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>266</v>
@@ -13042,39 +13042,39 @@
         <v>1</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="H77" s="1" t="s">
+        <v>2054</v>
+      </c>
+      <c r="I77" s="1" t="s">
         <v>2055</v>
       </c>
-      <c r="I77" s="1" t="s">
+      <c r="J77" s="1" t="s">
         <v>2056</v>
       </c>
-      <c r="J77" s="1" t="s">
+      <c r="K77" s="1" t="s">
         <v>2057</v>
       </c>
-      <c r="K77" s="1" t="s">
+      <c r="L77" s="1" t="s">
         <v>2058</v>
       </c>
-      <c r="L77" s="1" t="s">
+      <c r="M77" s="1" t="s">
         <v>2059</v>
       </c>
-      <c r="M77" s="1" t="s">
-        <v>2060</v>
-      </c>
       <c r="N77" s="1" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="P77" s="1" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>266</v>
@@ -13083,39 +13083,39 @@
         <v>1</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="M78" s="1" t="s">
+        <v>2060</v>
+      </c>
+      <c r="N78" s="1" t="s">
         <v>2061</v>
       </c>
-      <c r="N78" s="1" t="s">
-        <v>2062</v>
-      </c>
       <c r="O78" s="1" t="s">
+        <v>2065</v>
+      </c>
+      <c r="P78" s="1" t="s">
         <v>2066</v>
-      </c>
-      <c r="P78" s="1" t="s">
-        <v>2067</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>266</v>
@@ -13124,42 +13124,42 @@
         <v>1</v>
       </c>
       <c r="G79" s="1" t="s">
+        <v>2053</v>
+      </c>
+      <c r="H79" s="1" t="s">
         <v>2054</v>
       </c>
-      <c r="H79" s="1" t="s">
-        <v>2055</v>
-      </c>
       <c r="I79" s="1" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="M79" s="1" t="s">
+        <v>2062</v>
+      </c>
+      <c r="N79" s="1" t="s">
+        <v>2061</v>
+      </c>
+      <c r="O79" s="1" t="s">
         <v>2063</v>
       </c>
-      <c r="N79" s="1" t="s">
-        <v>2062</v>
-      </c>
-      <c r="O79" s="1" t="s">
-        <v>2064</v>
-      </c>
       <c r="P79" s="1" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A80" s="1" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="B80" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>102</v>
@@ -13168,18 +13168,18 @@
         <v>1</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A81" s="1" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="B81" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>102</v>
@@ -13188,15 +13188,15 @@
         <v>1</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="B82" s="7" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>102</v>
@@ -13205,10 +13205,10 @@
         <v>1</v>
       </c>
       <c r="G82" s="1" t="s">
+        <v>2078</v>
+      </c>
+      <c r="H82" s="1" t="s">
         <v>2079</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>2080</v>
       </c>
     </row>
   </sheetData>
@@ -13438,10 +13438,10 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F5" t="s">
         <v>1677</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1678</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>487</v>
@@ -13477,34 +13477,34 @@
     <row r="6" spans="2:31" ht="18" x14ac:dyDescent="0.45">
       <c r="C6" s="1"/>
       <c r="G6" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="H6" t="s">
         <v>1665</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" s="1" t="s">
         <v>1666</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>1667</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="1" t="s">
         <v>1668</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>1669</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>1670</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>493</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>495</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="X6" s="1" t="s">
         <v>1437</v>
@@ -13513,16 +13513,16 @@
         <v>1438</v>
       </c>
       <c r="Z6" s="1" t="s">
+        <v>1674</v>
+      </c>
+      <c r="AA6" s="1" t="s">
         <v>1675</v>
       </c>
-      <c r="AA6" s="1" t="s">
-        <v>1676</v>
-      </c>
       <c r="AB6" s="1" t="s">
+        <v>1672</v>
+      </c>
+      <c r="AC6" s="1" t="s">
         <v>1673</v>
-      </c>
-      <c r="AC6" s="1" t="s">
-        <v>1674</v>
       </c>
     </row>
     <row r="7" spans="2:31" ht="18" x14ac:dyDescent="0.45">
@@ -14419,28 +14419,28 @@
     <row r="36" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="C36" s="1"/>
       <c r="G36" s="15" t="s">
+        <v>1700</v>
+      </c>
+      <c r="H36" s="15" t="s">
         <v>1701</v>
       </c>
-      <c r="H36" s="15" t="s">
+      <c r="K36" s="1" t="s">
         <v>1702</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="L36" s="1" t="s">
         <v>1703</v>
       </c>
-      <c r="L36" s="1" t="s">
+      <c r="M36" s="1" t="s">
         <v>1704</v>
       </c>
-      <c r="M36" s="1" t="s">
+      <c r="N36" s="1" t="s">
         <v>1705</v>
       </c>
-      <c r="N36" s="1" t="s">
+      <c r="O36" s="1" t="s">
         <v>1706</v>
       </c>
-      <c r="O36" s="1" t="s">
+      <c r="P36" s="1" t="s">
         <v>1707</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>1708</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -14657,7 +14657,7 @@
     </row>
     <row r="45" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>102</v>
@@ -14666,22 +14666,22 @@
         <v>1</v>
       </c>
       <c r="G45" s="1" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>1814</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="M45" s="1" t="s">
         <v>1815</v>
       </c>
-      <c r="M45" s="1" t="s">
+      <c r="N45" t="s">
         <v>1816</v>
       </c>
-      <c r="N45" t="s">
+      <c r="O45" s="1" t="s">
         <v>1817</v>
       </c>
-      <c r="O45" s="1" t="s">
+      <c r="P45" s="1" t="s">
         <v>1818</v>
-      </c>
-      <c r="P45" s="1" t="s">
-        <v>1819</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -14733,7 +14733,7 @@
         <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>1179</v>
@@ -14762,7 +14762,7 @@
     </row>
     <row r="48" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>266</v>
@@ -14771,21 +14771,21 @@
         <v>1</v>
       </c>
       <c r="E48" s="1" t="s">
+        <v>1447</v>
+      </c>
+      <c r="F48" t="s">
         <v>1448</v>
       </c>
-      <c r="F48" t="s">
-        <v>1449</v>
-      </c>
       <c r="G48" s="1" t="s">
+        <v>1445</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>1446</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>1447</v>
       </c>
     </row>
     <row r="49" spans="2:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>266</v>
@@ -14794,21 +14794,21 @@
         <v>1</v>
       </c>
       <c r="E49" t="s">
+        <v>1458</v>
+      </c>
+      <c r="F49" t="s">
         <v>1459</v>
       </c>
-      <c r="F49" t="s">
-        <v>1460</v>
-      </c>
       <c r="G49" s="1" t="s">
+        <v>1456</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>1457</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>1458</v>
       </c>
     </row>
     <row r="50" spans="2:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>102</v>
@@ -14817,33 +14817,33 @@
         <v>1</v>
       </c>
       <c r="G50" s="1" t="s">
+        <v>1510</v>
+      </c>
+      <c r="H50" s="1" t="s">
         <v>1511</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="K50" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="M50" t="s">
         <v>1512</v>
       </c>
-      <c r="K50" s="1" t="s">
-        <v>1515</v>
-      </c>
-      <c r="L50" s="1" t="s">
+      <c r="N50" s="1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="O50" s="1" t="s">
         <v>1516</v>
       </c>
-      <c r="M50" t="s">
-        <v>1513</v>
-      </c>
-      <c r="N50" s="1" t="s">
-        <v>1514</v>
-      </c>
-      <c r="O50" s="1" t="s">
+      <c r="P50" s="1" t="s">
         <v>1517</v>
-      </c>
-      <c r="P50" s="1" t="s">
-        <v>1518</v>
       </c>
     </row>
     <row r="51" spans="2:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>1144</v>
@@ -14852,33 +14852,33 @@
         <v>1</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="F51" t="s">
+        <v>1528</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>1524</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>1525</v>
+      </c>
+      <c r="M51" t="s">
         <v>1529</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>1525</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>1526</v>
-      </c>
-      <c r="M51" t="s">
+      <c r="N51" s="1" t="s">
         <v>1530</v>
       </c>
-      <c r="N51" s="1" t="s">
+      <c r="O51" s="1" t="s">
         <v>1531</v>
       </c>
-      <c r="O51" s="1" t="s">
+      <c r="P51" s="1" t="s">
         <v>1532</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>1533</v>
       </c>
     </row>
     <row r="52" spans="2:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>102</v>
@@ -14887,10 +14887,10 @@
         <v>1</v>
       </c>
       <c r="G52" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>1621</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>1622</v>
       </c>
     </row>
     <row r="53" spans="2:16" ht="18" x14ac:dyDescent="0.45">
@@ -14901,30 +14901,30 @@
         <v>1</v>
       </c>
       <c r="E53" s="1" t="s">
+        <v>1793</v>
+      </c>
+      <c r="F53" t="s">
         <v>1794</v>
       </c>
-      <c r="F53" t="s">
-        <v>1795</v>
-      </c>
       <c r="G53" s="1" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>1789</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="M53" s="1" t="s">
+        <v>1791</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>1792</v>
+      </c>
+      <c r="O53" t="s">
         <v>1790</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>1792</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>1793</v>
-      </c>
-      <c r="O53" t="s">
-        <v>1791</v>
       </c>
     </row>
     <row r="54" spans="2:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>102</v>
@@ -14933,39 +14933,39 @@
         <v>1</v>
       </c>
       <c r="G54" s="1" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H54" s="1" t="s">
         <v>1796</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="I54" s="1" t="s">
         <v>1797</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="J54" s="1" t="s">
+        <v>1800</v>
+      </c>
+      <c r="K54" s="1" t="s">
         <v>1798</v>
       </c>
-      <c r="J54" s="1" t="s">
+      <c r="L54" s="1" t="s">
+        <v>1799</v>
+      </c>
+      <c r="M54" s="1" t="s">
         <v>1801</v>
       </c>
-      <c r="K54" s="1" t="s">
-        <v>1799</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>1800</v>
-      </c>
-      <c r="M54" s="1" t="s">
+      <c r="N54" s="1" t="s">
         <v>1802</v>
       </c>
-      <c r="N54" s="1" t="s">
-        <v>1803</v>
-      </c>
       <c r="O54" s="1" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="55" spans="2:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>102</v>
@@ -14974,39 +14974,39 @@
         <v>1</v>
       </c>
       <c r="G55" s="1" t="s">
+        <v>1807</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>1796</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>1808</v>
       </c>
-      <c r="H55" s="1" t="s">
-        <v>1797</v>
-      </c>
-      <c r="I55" s="1" t="s">
+      <c r="J55" s="1" t="s">
+        <v>1800</v>
+      </c>
+      <c r="K55" s="1" t="s">
         <v>1809</v>
       </c>
-      <c r="J55" s="1" t="s">
-        <v>1801</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>1810</v>
-      </c>
       <c r="L55" s="1" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="N55" s="1" t="s">
+        <v>1802</v>
+      </c>
+      <c r="O55" s="1" t="s">
         <v>1803</v>
       </c>
-      <c r="O55" s="1" t="s">
+      <c r="P55" s="1" t="s">
         <v>1804</v>
-      </c>
-      <c r="P55" s="1" t="s">
-        <v>1805</v>
       </c>
     </row>
     <row r="56" spans="2:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>1144</v>
@@ -15015,39 +15015,39 @@
         <v>1</v>
       </c>
       <c r="G56" s="1" t="s">
+        <v>2006</v>
+      </c>
+      <c r="H56" s="1" t="s">
         <v>2007</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="I56" s="1" t="s">
         <v>2008</v>
       </c>
-      <c r="I56" s="1" t="s">
+      <c r="J56" s="1" t="s">
         <v>2009</v>
       </c>
-      <c r="J56" s="1" t="s">
+      <c r="K56" s="1" t="s">
         <v>2010</v>
       </c>
-      <c r="K56" s="1" t="s">
+      <c r="L56" s="1" t="s">
         <v>2011</v>
       </c>
-      <c r="L56" s="1" t="s">
+      <c r="M56" s="1" t="s">
         <v>2012</v>
       </c>
-      <c r="M56" s="1" t="s">
+      <c r="N56" s="1" t="s">
         <v>2013</v>
       </c>
-      <c r="N56" s="1" t="s">
+      <c r="O56" s="1" t="s">
         <v>2014</v>
       </c>
-      <c r="O56" s="1" t="s">
+      <c r="P56" s="1" t="s">
         <v>2015</v>
-      </c>
-      <c r="P56" s="1" t="s">
-        <v>2016</v>
       </c>
     </row>
     <row r="57" spans="2:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>102</v>
@@ -15056,34 +15056,34 @@
         <v>2</v>
       </c>
       <c r="G57" t="s">
+        <v>2040</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>2041</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="I57" s="1" t="s">
         <v>2042</v>
       </c>
-      <c r="I57" s="1" t="s">
+      <c r="J57" s="1" t="s">
         <v>2043</v>
       </c>
-      <c r="J57" s="1" t="s">
+      <c r="K57" s="1" t="s">
+        <v>2046</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>2047</v>
+      </c>
+      <c r="M57" s="1" t="s">
         <v>2044</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>2047</v>
-      </c>
-      <c r="L57" s="1" t="s">
+      <c r="N57" s="1" t="s">
+        <v>2045</v>
+      </c>
+      <c r="O57" s="1" t="s">
         <v>2048</v>
       </c>
-      <c r="M57" s="1" t="s">
-        <v>2045</v>
-      </c>
-      <c r="N57" s="1" t="s">
-        <v>2046</v>
-      </c>
-      <c r="O57" s="1" t="s">
+      <c r="P57" s="1" t="s">
         <v>2049</v>
-      </c>
-      <c r="P57" s="1" t="s">
-        <v>2050</v>
       </c>
     </row>
   </sheetData>
@@ -15463,7 +15463,7 @@
     </row>
     <row r="11" spans="1:31" ht="18" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="B11" t="s">
         <v>761</v>
@@ -15481,10 +15481,10 @@
         <v>760</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>1897</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>1898</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>1899</v>
       </c>
       <c r="M11" t="s">
         <v>1367</v>
@@ -15504,13 +15504,13 @@
         <v>1087</v>
       </c>
       <c r="B12" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>1880</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="D12" t="s">
         <v>1881</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1882</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>102</v>
@@ -15519,28 +15519,28 @@
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
+        <v>1877</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>1878</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>1879</v>
-      </c>
       <c r="I12" s="1" t="s">
+        <v>1882</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>1883</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>1884</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="N12" s="1" t="s">
         <v>1885</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="O12" s="1" t="s">
         <v>1886</v>
       </c>
-      <c r="O12" s="1" t="s">
+      <c r="P12" s="1" t="s">
         <v>1887</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>1888</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="18" x14ac:dyDescent="0.45">
@@ -15560,7 +15560,7 @@
         <v>763</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>764</v>
@@ -15797,13 +15797,13 @@
     <row r="21" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A21" s="1"/>
       <c r="B21" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D21" t="s">
         <v>1461</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1462</v>
       </c>
       <c r="E21" t="s">
         <v>266</v>
@@ -15812,28 +15812,28 @@
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>1463</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>1462</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>1464</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>1463</v>
-      </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>1465</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="M21" s="1" t="s">
         <v>1466</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="N21" s="1" t="s">
         <v>1467</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="O21" s="1" t="s">
         <v>1468</v>
       </c>
-      <c r="O21" s="1" t="s">
+      <c r="P21" s="1" t="s">
         <v>1469</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>1470</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -15870,7 +15870,7 @@
         <v>876</v>
       </c>
       <c r="E23" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -15963,37 +15963,37 @@
     </row>
     <row r="26" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C26" t="s">
         <v>1479</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>1480</v>
       </c>
-      <c r="D26" t="s">
-        <v>1481</v>
-      </c>
       <c r="E26" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
+        <v>1472</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>1473</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="M26" s="1" t="s">
         <v>1474</v>
       </c>
-      <c r="M26" s="1" t="s">
+      <c r="N26" s="1" t="s">
         <v>1475</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="O26" s="1" t="s">
         <v>1476</v>
       </c>
-      <c r="O26" s="1" t="s">
+      <c r="P26" s="1" t="s">
         <v>1477</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>1478</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -16050,56 +16050,56 @@
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
+        <v>1966</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>1967</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="M29" s="1" t="s">
         <v>1968</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="N29" s="1" t="s">
         <v>1969</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="O29" s="1" t="s">
         <v>1970</v>
       </c>
-      <c r="O29" s="1" t="s">
+      <c r="P29" s="1" t="s">
         <v>1971</v>
-      </c>
-      <c r="P29" s="1" t="s">
-        <v>1972</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C30" t="s">
         <v>1594</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>1595</v>
       </c>
-      <c r="D30" t="s">
-        <v>1596</v>
-      </c>
       <c r="E30" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="F30">
         <v>2</v>
       </c>
       <c r="G30" s="1" t="s">
+        <v>1591</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>1592</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>1593</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="C31" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D31" t="s">
         <v>1603</v>
-      </c>
-      <c r="D31" t="s">
-        <v>1604</v>
       </c>
       <c r="E31" t="s">
         <v>266</v>
@@ -16108,33 +16108,33 @@
         <v>2</v>
       </c>
       <c r="G31" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>1597</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="M31" s="1" t="s">
         <v>1598</v>
       </c>
-      <c r="M31" s="1" t="s">
+      <c r="N31" s="1" t="s">
         <v>1599</v>
       </c>
-      <c r="N31" s="1" t="s">
+      <c r="O31" s="1" t="s">
+        <v>1601</v>
+      </c>
+      <c r="P31" s="1" t="s">
         <v>1600</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>1602</v>
-      </c>
-      <c r="P31" s="1" t="s">
-        <v>1601</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="C32" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="D32" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>1144</v>
@@ -16143,30 +16143,30 @@
         <v>2</v>
       </c>
       <c r="G32" s="1" t="s">
+        <v>1760</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>1761</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="M32" s="1" t="s">
         <v>1762</v>
       </c>
-      <c r="M32" s="1" t="s">
+      <c r="N32" s="1" t="s">
         <v>1763</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>1764</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="B33" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>1931</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="D33" t="s">
         <v>1932</v>
-      </c>
-      <c r="D33" t="s">
-        <v>1933</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>266</v>
@@ -16175,33 +16175,33 @@
         <v>2</v>
       </c>
       <c r="G33" s="1" t="s">
+        <v>1921</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>1922</v>
       </c>
-      <c r="H33" s="1" t="s">
-        <v>1923</v>
-      </c>
       <c r="I33" s="1" t="s">
+        <v>1928</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>1929</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>1930</v>
-      </c>
       <c r="M33" s="1" t="s">
+        <v>1924</v>
+      </c>
+      <c r="N33" s="1" t="s">
         <v>1925</v>
       </c>
-      <c r="N33" s="1" t="s">
+      <c r="O33" s="1" t="s">
         <v>1926</v>
       </c>
-      <c r="O33" s="1" t="s">
+      <c r="P33" s="1" t="s">
         <v>1927</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>1928</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>266</v>
@@ -16210,27 +16210,27 @@
         <v>2</v>
       </c>
       <c r="G34" s="1" t="s">
+        <v>1981</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>1982</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="M34" s="1" t="s">
         <v>1983</v>
       </c>
-      <c r="M34" s="1" t="s">
+      <c r="N34" s="1" t="s">
         <v>1984</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="O34" s="1" t="s">
         <v>1985</v>
       </c>
-      <c r="O34" s="1" t="s">
+      <c r="P34" s="1" t="s">
         <v>1986</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>1987</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>266</v>
@@ -16239,28 +16239,28 @@
         <v>2</v>
       </c>
       <c r="G35" s="1" t="s">
+        <v>1997</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>1998</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="K35" s="1" t="s">
+        <v>2004</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>2005</v>
+      </c>
+      <c r="M35" s="1" t="s">
         <v>1999</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>2005</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>2006</v>
-      </c>
-      <c r="M35" s="1" t="s">
+      <c r="N35" s="1" t="s">
         <v>2000</v>
       </c>
-      <c r="N35" s="1" t="s">
+      <c r="O35" s="1" t="s">
+        <v>2002</v>
+      </c>
+      <c r="P35" s="1" t="s">
         <v>2001</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>2003</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>2002</v>
       </c>
     </row>
   </sheetData>
@@ -16556,7 +16556,7 @@
         <v>1068</v>
       </c>
       <c r="C5" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="D5" t="s">
         <v>1070</v>
@@ -16568,54 +16568,54 @@
         <v>2</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>1933</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>1934</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="L5" s="1" t="s">
+        <v>1936</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>1935</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>1937</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>1936</v>
-      </c>
-      <c r="N5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>1938</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="1" t="s">
+        <v>1940</v>
+      </c>
+      <c r="Q5" s="1" t="s">
         <v>1939</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>1941</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="6" spans="1:32" ht="18" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>1518</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>1519</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>1520</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="O6" s="1" t="s">
+        <v>1522</v>
+      </c>
+      <c r="P6" s="1" t="s">
         <v>1521</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
         <v>1523</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>1522</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>1524</v>
       </c>
     </row>
   </sheetData>
@@ -16796,30 +16796,30 @@
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>1642</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>1643</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>1644</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1" t="s">
+        <v>1648</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>1649</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>1650</v>
-      </c>
       <c r="M3" s="1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>1657</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>1658</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>1659</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>1660</v>
       </c>
       <c r="Q3" s="1"/>
       <c r="R3" s="6"/>
@@ -16829,16 +16829,16 @@
       <c r="V3" s="6"/>
       <c r="W3" s="6"/>
       <c r="X3" s="16" t="s">
+        <v>1661</v>
+      </c>
+      <c r="Y3" s="16" t="s">
         <v>1662</v>
       </c>
-      <c r="Y3" s="16" t="s">
+      <c r="Z3" s="16" t="s">
+        <v>1660</v>
+      </c>
+      <c r="AA3" s="16" t="s">
         <v>1663</v>
-      </c>
-      <c r="Z3" s="16" t="s">
-        <v>1661</v>
-      </c>
-      <c r="AA3" s="16" t="s">
-        <v>1664</v>
       </c>
       <c r="AB3" s="6"/>
       <c r="AC3" s="6"/>
@@ -16853,34 +16853,34 @@
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>1644</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>1645</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>1646</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>1647</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>1648</v>
-      </c>
       <c r="K4" s="1" t="s">
+        <v>1650</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>1651</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>1652</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>1653</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>1654</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>1655</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>1656</v>
       </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="6"/>
@@ -16900,7 +16900,7 @@
     </row>
     <row r="5" spans="1:31" ht="18" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="E5" t="s">
         <v>266</v>
@@ -16909,34 +16909,34 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>1835</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>1836</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>1837</v>
-      </c>
       <c r="I5" s="1" t="s">
+        <v>1841</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>1842</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>1843</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>1844</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>1845</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>1846</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>1847</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>1848</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>1849</v>
       </c>
       <c r="Q5" s="1"/>
       <c r="R5" s="6"/>
@@ -16946,16 +16946,16 @@
       <c r="V5" s="6"/>
       <c r="W5" s="6"/>
       <c r="X5" s="16" t="s">
+        <v>1839</v>
+      </c>
+      <c r="Y5" s="16" t="s">
         <v>1840</v>
       </c>
-      <c r="Y5" s="16" t="s">
-        <v>1841</v>
-      </c>
       <c r="Z5" s="16" t="s">
+        <v>1837</v>
+      </c>
+      <c r="AA5" s="16" t="s">
         <v>1838</v>
-      </c>
-      <c r="AA5" s="16" t="s">
-        <v>1839</v>
       </c>
       <c r="AB5" s="6"/>
       <c r="AC5" s="6"/>
@@ -16964,13 +16964,13 @@
     </row>
     <row r="6" spans="1:31" ht="18" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>1823</v>
+      </c>
+      <c r="D6" t="s">
         <v>1824</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1825</v>
       </c>
       <c r="E6" t="s">
         <v>266</v>
@@ -16985,24 +16985,24 @@
         <v>718</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>1819</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>1820</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>1821</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>1577</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="O6" s="1" t="s">
         <v>1578</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" s="1" t="s">
         <v>1579</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>1580</v>
       </c>
       <c r="Q6" s="1"/>
       <c r="R6" s="6"/>
@@ -17014,10 +17014,10 @@
       <c r="X6" s="17"/>
       <c r="Y6" s="17"/>
       <c r="Z6" s="16" t="s">
+        <v>1821</v>
+      </c>
+      <c r="AA6" s="17" t="s">
         <v>1822</v>
-      </c>
-      <c r="AA6" s="17" t="s">
-        <v>1823</v>
       </c>
       <c r="AB6" s="6"/>
       <c r="AC6" s="6"/>
@@ -17026,13 +17026,13 @@
     </row>
     <row r="7" spans="1:31" ht="18" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="D7" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>102</v>
@@ -17041,34 +17041,34 @@
         <v>2</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>1821</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>1822</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>1823</v>
-      </c>
       <c r="I7" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>1827</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
         <v>1828</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>1829</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>1830</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="N7" s="1" t="s">
         <v>1831</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="O7" s="1" t="s">
         <v>1832</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="P7" s="1" t="s">
         <v>1833</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>1834</v>
       </c>
       <c r="Q7" s="1"/>
       <c r="R7" s="6"/>
@@ -17259,7 +17259,7 @@
     <row r="11" spans="1:31" ht="18" x14ac:dyDescent="0.45">
       <c r="A11" s="1"/>
       <c r="B11" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>1144</v>
@@ -17268,37 +17268,37 @@
         <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
+        <v>1606</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>1607</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>1608</v>
-      </c>
       <c r="I11" s="1" t="s">
+        <v>1609</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>1610</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>1611</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>1612</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>1613</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="N11" s="1" t="s">
         <v>1614</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="O11" s="1" t="s">
         <v>1615</v>
       </c>
-      <c r="O11" s="1" t="s">
+      <c r="P11" s="1" t="s">
         <v>1616</v>
       </c>
-      <c r="P11" s="1" t="s">
+      <c r="Q11" s="1" t="s">
         <v>1617</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>1618</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
@@ -17311,10 +17311,10 @@
       <c r="Z11" s="1"/>
       <c r="AA11" s="1"/>
       <c r="AB11" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="AC11" s="1" t="s">
         <v>1619</v>
-      </c>
-      <c r="AC11" s="1" t="s">
-        <v>1620</v>
       </c>
       <c r="AD11" s="1"/>
       <c r="AE11" s="1"/>
@@ -17802,16 +17802,16 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1" t="s">
+        <v>1773</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>1770</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>1774</v>
       </c>
-      <c r="N26" s="1" t="s">
-        <v>1771</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>1775</v>
-      </c>
       <c r="P26" s="1" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="27" spans="2:16" ht="18" x14ac:dyDescent="0.45">
@@ -17830,16 +17830,16 @@
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="M27" s="1" t="s">
+        <v>1769</v>
+      </c>
+      <c r="N27" s="1" t="s">
         <v>1770</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="O27" s="1" t="s">
         <v>1771</v>
       </c>
-      <c r="O27" s="1" t="s">
+      <c r="P27" s="1" t="s">
         <v>1772</v>
-      </c>
-      <c r="P27" s="1" t="s">
-        <v>1773</v>
       </c>
     </row>
     <row r="28" spans="2:16" ht="18" x14ac:dyDescent="0.45">
@@ -17991,16 +17991,16 @@
         <v>25</v>
       </c>
       <c r="M32" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="N32" s="1" t="s">
         <v>1588</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="O32" s="1" t="s">
         <v>1589</v>
       </c>
-      <c r="O32" s="1" t="s">
+      <c r="P32" s="1" t="s">
         <v>1590</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>1591</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -18026,10 +18026,10 @@
         <v>1420</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -18061,10 +18061,10 @@
         <v>1420</v>
       </c>
       <c r="O34" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="P34" s="1" t="s">
         <v>1585</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>1586</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -18158,16 +18158,16 @@
         <v>710</v>
       </c>
       <c r="M39" t="s">
+        <v>1580</v>
+      </c>
+      <c r="N39" s="1" t="s">
         <v>1581</v>
       </c>
-      <c r="N39" s="1" t="s">
+      <c r="O39" s="1" t="s">
         <v>1582</v>
       </c>
-      <c r="O39" s="1" t="s">
+      <c r="P39" s="1" t="s">
         <v>1583</v>
-      </c>
-      <c r="P39" s="1" t="s">
-        <v>1584</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -18212,16 +18212,16 @@
         <v>718</v>
       </c>
       <c r="M41" s="1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="N41" s="1" t="s">
         <v>1577</v>
       </c>
-      <c r="N41" s="1" t="s">
+      <c r="O41" s="1" t="s">
         <v>1578</v>
       </c>
-      <c r="O41" s="1" t="s">
+      <c r="P41" s="1" t="s">
         <v>1579</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>1580</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -18257,16 +18257,16 @@
         <v>730</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="N43" t="s">
+        <v>1569</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>1575</v>
+      </c>
+      <c r="P43" s="1" t="s">
         <v>1570</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>1576</v>
-      </c>
-      <c r="P43" s="1" t="s">
-        <v>1571</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -18284,16 +18284,16 @@
         <v>730</v>
       </c>
       <c r="M44" s="1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="N44" t="s">
         <v>1569</v>
       </c>
-      <c r="N44" t="s">
+      <c r="O44" s="1" t="s">
+        <v>1574</v>
+      </c>
+      <c r="P44" s="1" t="s">
         <v>1570</v>
-      </c>
-      <c r="O44" s="1" t="s">
-        <v>1575</v>
-      </c>
-      <c r="P44" s="1" t="s">
-        <v>1571</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -18313,16 +18313,16 @@
         <v>730</v>
       </c>
       <c r="M45" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="N45" t="s">
+        <v>1569</v>
+      </c>
+      <c r="O45" s="1" t="s">
         <v>1573</v>
       </c>
-      <c r="N45" t="s">
+      <c r="P45" s="1" t="s">
         <v>1570</v>
-      </c>
-      <c r="O45" s="1" t="s">
-        <v>1574</v>
-      </c>
-      <c r="P45" s="1" t="s">
-        <v>1571</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -18391,16 +18391,16 @@
         <v>795</v>
       </c>
       <c r="M48" t="s">
+        <v>1564</v>
+      </c>
+      <c r="N48" s="1" t="s">
         <v>1565</v>
       </c>
-      <c r="N48" s="1" t="s">
+      <c r="O48" s="1" t="s">
         <v>1566</v>
       </c>
-      <c r="O48" s="1" t="s">
+      <c r="P48" s="1" t="s">
         <v>1567</v>
-      </c>
-      <c r="P48" s="1" t="s">
-        <v>1568</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -18446,16 +18446,16 @@
         <v>832</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="N50" s="1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="O50" s="1" t="s">
         <v>1554</v>
       </c>
-      <c r="O50" s="1" t="s">
+      <c r="P50" s="1" t="s">
         <v>1555</v>
-      </c>
-      <c r="P50" s="1" t="s">
-        <v>1556</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -18470,22 +18470,22 @@
         <v>1</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>832</v>
       </c>
       <c r="M51" s="1" t="s">
+        <v>1552</v>
+      </c>
+      <c r="N51" s="1" t="s">
         <v>1553</v>
       </c>
-      <c r="N51" s="1" t="s">
-        <v>1554</v>
-      </c>
       <c r="O51" s="1" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -18508,16 +18508,16 @@
         <v>840</v>
       </c>
       <c r="M52" s="1" t="s">
+        <v>1548</v>
+      </c>
+      <c r="N52" s="1" t="s">
         <v>1549</v>
       </c>
-      <c r="N52" s="1" t="s">
+      <c r="O52" s="1" t="s">
         <v>1550</v>
       </c>
-      <c r="O52" s="1" t="s">
+      <c r="P52" s="1" t="s">
         <v>1551</v>
-      </c>
-      <c r="P52" s="1" t="s">
-        <v>1552</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -18593,7 +18593,7 @@
         <v>1361</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="O55" s="1" t="s">
         <v>1363</v>
@@ -18687,16 +18687,16 @@
         <v>949</v>
       </c>
       <c r="M58" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="N58" s="1" t="s">
         <v>1560</v>
       </c>
-      <c r="N58" s="1" t="s">
+      <c r="O58" s="1" t="s">
         <v>1561</v>
       </c>
-      <c r="O58" s="1" t="s">
+      <c r="P58" s="1" t="s">
         <v>1562</v>
-      </c>
-      <c r="P58" s="1" t="s">
-        <v>1563</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -18823,16 +18823,16 @@
         <v>941</v>
       </c>
       <c r="M62" s="1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="N62" s="1" t="s">
         <v>1545</v>
       </c>
-      <c r="N62" s="1" t="s">
+      <c r="O62" s="1" t="s">
         <v>1546</v>
       </c>
-      <c r="O62" s="1" t="s">
+      <c r="P62" s="1" t="s">
         <v>1547</v>
-      </c>
-      <c r="P62" s="1" t="s">
-        <v>1548</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -19067,16 +19067,16 @@
         <v>29</v>
       </c>
       <c r="M74" s="1" t="s">
+        <v>1540</v>
+      </c>
+      <c r="N74" t="s">
         <v>1541</v>
       </c>
-      <c r="N74" t="s">
+      <c r="O74" t="s">
         <v>1542</v>
       </c>
-      <c r="O74" t="s">
+      <c r="P74" s="1" t="s">
         <v>1543</v>
-      </c>
-      <c r="P74" s="1" t="s">
-        <v>1544</v>
       </c>
     </row>
     <row r="75" spans="1:16" ht="18" x14ac:dyDescent="0.45">
@@ -19121,7 +19121,7 @@
     </row>
     <row r="77" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="E77" t="s">
         <v>266</v>
@@ -19150,7 +19150,7 @@
     </row>
     <row r="78" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="E78" t="s">
         <v>266</v>
@@ -19159,15 +19159,15 @@
         <v>1</v>
       </c>
       <c r="G78" s="1" t="s">
+        <v>1481</v>
+      </c>
+      <c r="H78" s="1" t="s">
         <v>1482</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>1483</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="E79" t="s">
         <v>266</v>
@@ -19176,27 +19176,27 @@
         <v>1</v>
       </c>
       <c r="G79" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="H79" s="1" t="s">
         <v>1485</v>
       </c>
-      <c r="H79" s="1" t="s">
-        <v>1486</v>
-      </c>
       <c r="M79" s="1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="N79" t="s">
         <v>1488</v>
       </c>
-      <c r="N79" t="s">
+      <c r="O79" t="s">
         <v>1489</v>
       </c>
-      <c r="O79" t="s">
+      <c r="P79" s="1" t="s">
         <v>1490</v>
-      </c>
-      <c r="P79" s="1" t="s">
-        <v>1491</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="E80" t="s">
         <v>266</v>
@@ -19205,33 +19205,33 @@
         <v>1</v>
       </c>
       <c r="G80" s="1" t="s">
+        <v>1533</v>
+      </c>
+      <c r="H80" s="1" t="s">
         <v>1534</v>
       </c>
-      <c r="H80" s="1" t="s">
-        <v>1535</v>
-      </c>
       <c r="M80" s="1" t="s">
+        <v>1536</v>
+      </c>
+      <c r="N80" t="s">
         <v>1537</v>
       </c>
-      <c r="N80" t="s">
+      <c r="O80" t="s">
+        <v>1539</v>
+      </c>
+      <c r="P80" t="s">
         <v>1538</v>
-      </c>
-      <c r="O80" t="s">
-        <v>1540</v>
-      </c>
-      <c r="P80" t="s">
-        <v>1539</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="C81" s="1" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D81" t="s">
         <v>1635</v>
-      </c>
-      <c r="D81" t="s">
-        <v>1636</v>
       </c>
       <c r="E81" t="s">
         <v>266</v>
@@ -19240,33 +19240,33 @@
         <v>1</v>
       </c>
       <c r="G81" s="1" t="s">
+        <v>1632</v>
+      </c>
+      <c r="H81" s="1" t="s">
         <v>1633</v>
       </c>
-      <c r="H81" s="1" t="s">
-        <v>1634</v>
-      </c>
       <c r="M81" s="1" t="s">
+        <v>1709</v>
+      </c>
+      <c r="N81" s="1" t="s">
         <v>1710</v>
       </c>
-      <c r="N81" s="1" t="s">
+      <c r="O81" s="1" t="s">
         <v>1711</v>
       </c>
-      <c r="O81" s="1" t="s">
+      <c r="P81" s="1" t="s">
         <v>1712</v>
-      </c>
-      <c r="P81" s="1" t="s">
-        <v>1713</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="C82" s="1" t="s">
+        <v>1766</v>
+      </c>
+      <c r="D82" t="s">
         <v>1767</v>
-      </c>
-      <c r="D82" t="s">
-        <v>1768</v>
       </c>
       <c r="E82" t="s">
         <v>266</v>
@@ -19275,30 +19275,30 @@
         <v>1</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="M82" s="1" t="s">
+        <v>1713</v>
+      </c>
+      <c r="N82" s="1" t="s">
         <v>1714</v>
       </c>
-      <c r="N82" s="1" t="s">
+      <c r="O82" s="1" t="s">
         <v>1715</v>
       </c>
-      <c r="O82" s="1" t="s">
+      <c r="P82" s="1" t="s">
         <v>1716</v>
-      </c>
-      <c r="P82" s="1" t="s">
-        <v>1717</v>
       </c>
     </row>
     <row r="83" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="A83" s="1" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="B83" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="E83" t="s">
         <v>266</v>
@@ -19307,33 +19307,33 @@
         <v>2</v>
       </c>
       <c r="G83" s="1" t="s">
+        <v>1720</v>
+      </c>
+      <c r="H83" s="1" t="s">
         <v>1721</v>
       </c>
-      <c r="H83" s="1" t="s">
-        <v>1722</v>
-      </c>
       <c r="M83" s="1" t="s">
+        <v>1723</v>
+      </c>
+      <c r="N83" s="1" t="s">
         <v>1724</v>
       </c>
-      <c r="N83" s="1" t="s">
-        <v>1725</v>
-      </c>
       <c r="O83" s="1" t="s">
+        <v>1726</v>
+      </c>
+      <c r="P83" s="1" t="s">
         <v>1727</v>
-      </c>
-      <c r="P83" s="1" t="s">
-        <v>1728</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B84" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C84" t="s">
         <v>1895</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>1896</v>
-      </c>
-      <c r="D84" t="s">
-        <v>1897</v>
       </c>
       <c r="E84" t="s">
         <v>266</v>
@@ -19342,33 +19342,33 @@
         <v>2</v>
       </c>
       <c r="G84" s="1" t="s">
+        <v>1888</v>
+      </c>
+      <c r="H84" s="1" t="s">
         <v>1889</v>
       </c>
-      <c r="H84" s="1" t="s">
+      <c r="M84" s="1" t="s">
         <v>1890</v>
       </c>
-      <c r="M84" s="1" t="s">
+      <c r="N84" s="1" t="s">
         <v>1891</v>
       </c>
-      <c r="N84" s="1" t="s">
+      <c r="O84" s="1" t="s">
         <v>1892</v>
       </c>
-      <c r="O84" s="1" t="s">
+      <c r="P84" s="1" t="s">
         <v>1893</v>
-      </c>
-      <c r="P84" s="1" t="s">
-        <v>1894</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>712</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="E85" t="s">
         <v>266</v>
@@ -19383,21 +19383,21 @@
         <v>3</v>
       </c>
       <c r="M85" s="1" t="s">
+        <v>1943</v>
+      </c>
+      <c r="N85" s="1" t="s">
         <v>1944</v>
       </c>
-      <c r="N85" s="1" t="s">
+      <c r="O85" s="1" t="s">
         <v>1945</v>
       </c>
-      <c r="O85" s="1" t="s">
+      <c r="P85" s="1" t="s">
         <v>1946</v>
-      </c>
-      <c r="P85" s="1" t="s">
-        <v>1947</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B86" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E86" t="s">
         <v>266</v>
@@ -19406,27 +19406,27 @@
         <v>2</v>
       </c>
       <c r="G86" s="1" t="s">
+        <v>2017</v>
+      </c>
+      <c r="H86" s="1" t="s">
         <v>2018</v>
       </c>
-      <c r="H86" s="1" t="s">
+      <c r="M86" s="1" t="s">
         <v>2019</v>
       </c>
-      <c r="M86" s="1" t="s">
+      <c r="N86" s="1" t="s">
         <v>2020</v>
       </c>
-      <c r="N86" s="1" t="s">
+      <c r="O86" s="1" t="s">
         <v>2021</v>
       </c>
-      <c r="O86" s="1" t="s">
+      <c r="P86" s="1" t="s">
         <v>2022</v>
-      </c>
-      <c r="P86" s="1" t="s">
-        <v>2023</v>
       </c>
     </row>
     <row r="87" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B87" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E87" t="s">
         <v>266</v>
@@ -19435,21 +19435,21 @@
         <v>1</v>
       </c>
       <c r="G87" t="s">
+        <v>2025</v>
+      </c>
+      <c r="H87" s="1" t="s">
         <v>2026</v>
       </c>
-      <c r="H87" s="1" t="s">
+      <c r="N87" s="1" t="s">
         <v>2027</v>
       </c>
-      <c r="N87" s="1" t="s">
+      <c r="P87" s="1" t="s">
         <v>2028</v>
-      </c>
-      <c r="P87" s="1" t="s">
-        <v>2029</v>
       </c>
     </row>
     <row r="88" spans="1:16" ht="18" x14ac:dyDescent="0.45">
       <c r="B88" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="E88" t="s">
         <v>266</v>
@@ -19458,10 +19458,10 @@
         <v>1</v>
       </c>
       <c r="G88" s="1" t="s">
+        <v>2029</v>
+      </c>
+      <c r="H88" s="1" t="s">
         <v>2030</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>2031</v>
       </c>
     </row>
   </sheetData>
@@ -19638,7 +19638,7 @@
         <v>1016</v>
       </c>
       <c r="B3" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1422</v>
@@ -19682,13 +19682,13 @@
     </row>
     <row r="4" spans="1:32" ht="18" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>1640</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" t="s">
         <v>1641</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1642</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>102</v>
@@ -19697,21 +19697,21 @@
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>1636</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>1637</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>1638</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="18" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D5" t="s">
         <v>1862</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1863</v>
       </c>
       <c r="E5" t="s">
         <v>266</v>
@@ -19720,36 +19720,36 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>1864</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>1865</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>1866</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>1867</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>1868</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>1869</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>1870</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="Q5" s="1" t="s">
         <v>1871</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>1872</v>
       </c>
     </row>
     <row r="6" spans="1:32" ht="18" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="D6" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>102</v>
@@ -19758,28 +19758,28 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>1972</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>1973</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>1974</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>1975</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>1976</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="O6" s="1" t="s">
         <v>1977</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" s="1" t="s">
         <v>1978</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
         <v>1979</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>1980</v>
       </c>
     </row>
   </sheetData>
